--- a/ARM Functions/Ability Edits/Orichalcum Body (Heatproof).xlsx
+++ b/ARM Functions/Ability Edits/Orichalcum Body (Heatproof).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Ability Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51208DE0-1051-4229-B5E1-A3F2890BC099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5FDBE3-9A19-4DAA-A00B-88099145081A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16457" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{DFD0B34E-FAAD-4BE6-8FC0-3053B30C3017}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16466" windowHeight="17914" xr2:uid="{DFD0B34E-FAAD-4BE6-8FC0-3053B30C3017}"/>
   </bookViews>
   <sheets>
     <sheet name="Heatproof" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="179">
   <si>
     <t>pop {r4, r5, r6, r7, r8, pc}</t>
   </si>
@@ -299,15 +299,6 @@
     <t>Call Function</t>
   </si>
   <si>
-    <t>000D7860</t>
-  </si>
-  <si>
-    <t>0310A0E3</t>
-  </si>
-  <si>
-    <t>mov r1, 0x3</t>
-  </si>
-  <si>
     <t>001080E5</t>
   </si>
   <si>
@@ -392,12 +383,6 @@
     <t>Apply ignore -attack-debuff flag if has major status</t>
   </si>
   <si>
-    <t>mov r1, 0x1800</t>
-  </si>
-  <si>
-    <t>mov r0, 0x39</t>
-  </si>
-  <si>
     <t>mov r0, 0x2</t>
   </si>
   <si>
@@ -458,12 +443,6 @@
     <t>5800A0E3</t>
   </si>
   <si>
-    <t>061BA0E3</t>
-  </si>
-  <si>
-    <t>3900A0E3</t>
-  </si>
-  <si>
     <t>Immune Poison 0x3A</t>
   </si>
   <si>
@@ -503,9 +482,6 @@
     <t>6713FEEB</t>
   </si>
   <si>
-    <t>000FE5B4</t>
-  </si>
-  <si>
     <t>mov r1, r2</t>
   </si>
   <si>
@@ -539,76 +515,64 @@
     <t>7B16FEEA</t>
   </si>
   <si>
-    <t>Add STAB for Fire and Steel 0x54</t>
-  </si>
-  <si>
-    <t>push {r4, lr}</t>
-  </si>
-  <si>
-    <t>check self</t>
-  </si>
-  <si>
-    <t>mov r0, 0x49</t>
-  </si>
-  <si>
-    <t>Check if STAB</t>
-  </si>
-  <si>
-    <t>if STAB do nothing</t>
-  </si>
-  <si>
-    <t>10402DE9</t>
-  </si>
-  <si>
-    <t>4900A0E3</t>
-  </si>
-  <si>
-    <t>1040BDE8</t>
-  </si>
-  <si>
-    <t>1080BDE8</t>
-  </si>
-  <si>
     <t>000DDF4C</t>
   </si>
   <si>
-    <t>FEA6FEEB</t>
-  </si>
-  <si>
-    <t>0D00001A</t>
-  </si>
-  <si>
-    <t>FAA6FEEB</t>
-  </si>
-  <si>
-    <t>1200A0E3</t>
-  </si>
-  <si>
-    <t>mov r0, 0x12</t>
-  </si>
-  <si>
-    <t>Get type</t>
-  </si>
-  <si>
-    <t>F6A6FEEB</t>
-  </si>
-  <si>
-    <t>9588FCEB</t>
-  </si>
-  <si>
-    <t>bl 0x000001D8</t>
-  </si>
-  <si>
-    <t>08005013</t>
-  </si>
-  <si>
-    <t>cmpne r0, 0x8</t>
-  </si>
-  <si>
     <t>Steel</t>
   </si>
   <si>
-    <t>6993FEEA</t>
+    <t>000FE300</t>
+  </si>
+  <si>
+    <t>Set Defensive Steel 0x6D/0xA7/0x6A</t>
+  </si>
+  <si>
+    <t>000FE308</t>
+  </si>
+  <si>
+    <t>000D84C0</t>
+  </si>
+  <si>
+    <t>mov r1, 0xA</t>
+  </si>
+  <si>
+    <t>0A10A0E3</t>
+  </si>
+  <si>
+    <t>Add STAB for Fire and Steel 0x5B</t>
+  </si>
+  <si>
+    <t>push {lr}</t>
+  </si>
+  <si>
+    <t>mov r0, 0x9</t>
+  </si>
+  <si>
+    <t>b 0x001032EC</t>
+  </si>
+  <si>
+    <t>bl 0x001032EC</t>
+  </si>
+  <si>
+    <t>mov r0, 0x8</t>
+  </si>
+  <si>
+    <t>04E02DE5</t>
+  </si>
+  <si>
+    <t>0900A0E3</t>
+  </si>
+  <si>
+    <t>E49400EB</t>
+  </si>
+  <si>
+    <t>04E09DE4</t>
+  </si>
+  <si>
+    <t>0800A0E3</t>
+  </si>
+  <si>
+    <t>E19400EA</t>
   </si>
 </sst>
 </file>
@@ -686,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -736,8 +700,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1072,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D5FF14-B243-47B9-B921-E1E0A4F7D67F}">
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -1108,65 +1073,65 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>89</v>
+        <v>165</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2" t="str">
         <f t="shared" ref="A4:A7" si="0">DEC2HEX(HEX2DEC(A3)+4,8)</f>
-        <v>000D7864</v>
+        <v>000D84C4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>000D7868</v>
+        <v>000D84C8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>000D786C</v>
+        <v>000D84CC</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D6" s="1"/>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>000D7870</v>
+        <v>000D84D0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -1175,7 +1140,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B9" s="4"/>
     </row>
@@ -1223,10 +1188,10 @@
         <v>50</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1262,7 +1227,7 @@
         <v>000DB338</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C16" s="5" t="str">
         <f>_xlfn.CONCAT("bne  0x",A$48)</f>
@@ -1282,7 +1247,7 @@
         <v>46</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1330,7 +1295,7 @@
         <v>000DB34C</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C21" s="9" t="str">
         <f>_xlfn.CONCAT("bne  0x",A$48)</f>
@@ -1368,7 +1333,7 @@
         <v>000DB358</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>38</v>
@@ -1416,7 +1381,7 @@
         <v>000DB368</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>31</v>
@@ -1464,7 +1429,7 @@
         <v>000DB378</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>26</v>
@@ -1488,7 +1453,7 @@
         <v>000DB380</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>84</v>
@@ -1515,7 +1480,7 @@
         <v>000DB388</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>21</v>
@@ -1635,7 +1600,7 @@
         <v>000DB3B0</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>2</v>
@@ -1646,7 +1611,7 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>1</v>
@@ -1655,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -1664,7 +1629,7 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1675,10 +1640,10 @@
         <v>65</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -1715,10 +1680,10 @@
         <v>66</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -1727,10 +1692,10 @@
         <v>000FD260</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D55" s="5"/>
       <c r="F55" s="14"/>
@@ -1754,7 +1719,7 @@
         <v>000FD268</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C57" s="5" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$66)</f>
@@ -1771,10 +1736,10 @@
         <v>61</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="19"/>
@@ -1786,10 +1751,10 @@
         <v>000FD270</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="8"/>
@@ -1805,7 +1770,7 @@
         <v>60</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>71</v>
@@ -1832,13 +1797,13 @@
         <v>000FD27C</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>85</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E62" s="3"/>
     </row>
@@ -1860,7 +1825,7 @@
         <v>000FD284</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C64" s="2" t="str">
         <f>SUBSTITUTE(C51,"push","pop")</f>
@@ -1873,10 +1838,10 @@
         <v>000FD288</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1885,7 +1850,7 @@
         <v>000FD28C</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C66" s="2" t="str">
         <f>SUBSTITUTE(C64,"lr","pc")</f>
@@ -1897,7 +1862,7 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B68" s="4"/>
     </row>
@@ -1907,10 +1872,10 @@
         <v>000FD290</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1946,10 +1911,10 @@
         <v>64</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1958,10 +1923,10 @@
         <v>000FD2A0</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D73" s="5"/>
     </row>
@@ -1984,7 +1949,7 @@
         <v>000FD2A8</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C75" s="5" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$86)</f>
@@ -2004,7 +1969,7 @@
         <v>7</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2026,7 +1991,7 @@
         <v>000FD2B4</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>57</v>
@@ -2039,13 +2004,13 @@
         <v>000FD2B8</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C79" s="21" t="s">
         <v>56</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2054,10 +2019,10 @@
         <v>000FD2BC</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D80" s="21"/>
     </row>
@@ -2067,7 +2032,7 @@
         <v>000FD2C0</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C81" s="21" t="str">
         <f>_xlfn.CONCAT("beq 0x",A86)</f>
@@ -2081,13 +2046,13 @@
         <v>000FD2C4</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C82" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="D82" s="24" t="s">
         <v>114</v>
-      </c>
-      <c r="D82" s="24" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2096,10 +2061,10 @@
         <v>000FD2C8</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D83" s="24"/>
     </row>
@@ -2109,7 +2074,7 @@
         <v>000FD2CC</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C84" s="2" t="str">
         <f>SUBSTITUTE(C69,"push","pop")</f>
@@ -2122,10 +2087,10 @@
         <v>000FD2D0</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2134,7 +2099,7 @@
         <v>000FD2D4</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C86" s="2" t="str">
         <f>SUBSTITUTE(C84,"lr","pc")</f>
@@ -2146,19 +2111,19 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B88" s="4"/>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2167,10 +2132,10 @@
         <v>000FD2DC</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2179,13 +2144,13 @@
         <v>000FD2E0</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2194,13 +2159,13 @@
         <v>000FD2E4</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2208,301 +2173,219 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B94" s="4"/>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B98" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B101" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C101" s="27" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="2" t="str">
-        <f t="shared" ref="A99:A118" si="6">DEC2HEX(HEX2DEC(A98)+4,8)</f>
+      <c r="D101" s="27"/>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="27" t="str">
+        <f t="shared" ref="A102:A106" si="6">DEC2HEX(HEX2DEC(A101)+4,8)</f>
         <v>000DDF50</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="5" t="str">
+      <c r="B102" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C102" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="D102" s="27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="27" t="str">
         <f t="shared" si="6"/>
         <v>000DDF54</v>
       </c>
-      <c r="B100" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="5" t="str">
+      <c r="B103" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C103" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="D103" s="27"/>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="27" t="str">
         <f t="shared" si="6"/>
         <v>000DDF58</v>
       </c>
-      <c r="B101" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D101" s="5"/>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="5" t="str">
+      <c r="B104" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C104" s="27" t="str">
+        <f>SUBSTITUTE(C101,"push","pop")</f>
+        <v>pop {lr}</v>
+      </c>
+      <c r="D104" s="27"/>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="27" t="str">
         <f t="shared" si="6"/>
         <v>000DDF5C</v>
       </c>
-      <c r="B102" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D102" s="5"/>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="5" t="str">
+      <c r="B105" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C105" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="D105" s="27" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="27" t="str">
         <f t="shared" si="6"/>
         <v>000DDF60</v>
       </c>
-      <c r="B103" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C103" s="5" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$118)</f>
-        <v>bne 0x000DDF9C</v>
-      </c>
-      <c r="D103" s="5"/>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="9" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF64</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C104" s="9" t="s">
+      <c r="B106" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C106" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="D104" s="9" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="9" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF68</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C105" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D105" s="9"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="9" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF6C</v>
-      </c>
-      <c r="B106" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C106" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D106" s="9"/>
+      <c r="D106" s="27"/>
     </row>
     <row r="107" spans="1:4">
-      <c r="A107" s="9" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF70</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="C107" s="9" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$118)</f>
-        <v>bne 0x000DDF9C</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>172</v>
-      </c>
+      <c r="A107" s="27"/>
+      <c r="B107" s="27"/>
+      <c r="C107" s="27"/>
+      <c r="D107" s="27"/>
     </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF74</v>
-      </c>
-      <c r="B108" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="C108" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="D108" s="21" t="s">
-        <v>183</v>
-      </c>
+      <c r="A108" s="27"/>
+      <c r="B108" s="27"/>
+      <c r="C108" s="27"/>
+      <c r="D108" s="27"/>
     </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF78</v>
-      </c>
-      <c r="B109" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C109" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D109" s="21"/>
+      <c r="A109" s="27"/>
+      <c r="B109" s="27"/>
+      <c r="C109" s="27"/>
+      <c r="D109" s="27"/>
     </row>
     <row r="110" spans="1:4">
-      <c r="A110" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF7C</v>
-      </c>
-      <c r="B110" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="C110" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="D110" s="21"/>
+      <c r="A110" s="27"/>
+      <c r="B110" s="28"/>
+      <c r="C110" s="27"/>
+      <c r="D110" s="27"/>
     </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF80</v>
-      </c>
-      <c r="B111" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C111" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="D111" s="21" t="s">
-        <v>71</v>
-      </c>
+      <c r="A111" s="27"/>
+      <c r="B111" s="27"/>
+      <c r="C111" s="27"/>
+      <c r="D111" s="27"/>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF84</v>
-      </c>
-      <c r="B112" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="C112" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D112" s="21" t="s">
-        <v>189</v>
-      </c>
+      <c r="A112" s="27"/>
+      <c r="B112" s="28"/>
+      <c r="C112" s="28"/>
+      <c r="D112" s="27"/>
     </row>
     <row r="113" spans="1:4">
-      <c r="A113" s="21" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF88</v>
-      </c>
-      <c r="B113" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C113" s="21" t="str">
-        <f>_xlfn.CONCAT("bne 0x",A$118)</f>
-        <v>bne 0x000DDF9C</v>
-      </c>
-      <c r="D113" s="21"/>
+      <c r="A113" s="27"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="27"/>
+      <c r="D113" s="27"/>
     </row>
     <row r="114" spans="1:4">
-      <c r="A114" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF8C</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>118</v>
-      </c>
+      <c r="A114" s="27"/>
+      <c r="B114" s="29"/>
+      <c r="C114" s="27"/>
+      <c r="D114" s="27"/>
     </row>
     <row r="115" spans="1:4">
-      <c r="A115" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF90</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>119</v>
-      </c>
+      <c r="A115" s="27"/>
+      <c r="B115" s="28"/>
+      <c r="C115" s="27"/>
+      <c r="D115" s="27"/>
     </row>
     <row r="116" spans="1:4">
-      <c r="A116" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF94</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C116" s="2" t="str">
-        <f>SUBSTITUTE(C98,"push","pop")</f>
-        <v>pop {r4, lr}</v>
-      </c>
+      <c r="A116" s="27"/>
+      <c r="B116" s="28"/>
+      <c r="C116" s="27"/>
+      <c r="D116" s="27"/>
     </row>
     <row r="117" spans="1:4">
-      <c r="A117" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF98</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>159</v>
-      </c>
+      <c r="A117" s="27"/>
+      <c r="B117" s="27"/>
+      <c r="C117" s="27"/>
+      <c r="D117" s="27"/>
     </row>
     <row r="118" spans="1:4">
-      <c r="A118" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>000DDF9C</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C118" s="2" t="str">
-        <f>SUBSTITUTE(C116,"lr","pc")</f>
-        <v>pop {r4, pc}</v>
-      </c>
+      <c r="A118" s="27"/>
+      <c r="B118" s="27"/>
+      <c r="C118" s="27"/>
+      <c r="D118" s="27"/>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="27"/>
+      <c r="B119" s="27"/>
+      <c r="C119" s="27"/>
+      <c r="D119" s="27"/>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="27"/>
+      <c r="B120" s="27"/>
+      <c r="C120" s="27"/>
+      <c r="D120" s="27"/>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="27"/>
+      <c r="B121" s="27"/>
+      <c r="C121" s="27"/>
+      <c r="D121" s="27"/>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="27"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="27"/>
+      <c r="D122" s="27"/>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="27"/>
+      <c r="B123" s="27"/>
+      <c r="C123" s="27"/>
+      <c r="D123" s="27"/>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="27"/>
+      <c r="B124" s="27"/>
+      <c r="C124" s="27"/>
+      <c r="D124" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ARM Functions/Ability Edits/Orichalcum Body (Heatproof).xlsx
+++ b/ARM Functions/Ability Edits/Orichalcum Body (Heatproof).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Ability Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5FDBE3-9A19-4DAA-A00B-88099145081A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A540D289-15C6-49DF-B389-127093A6DC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16466" windowHeight="17914" xr2:uid="{DFD0B34E-FAAD-4BE6-8FC0-3053B30C3017}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{DFD0B34E-FAAD-4BE6-8FC0-3053B30C3017}"/>
   </bookViews>
   <sheets>
     <sheet name="Heatproof" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="202">
   <si>
     <t>pop {r4, r5, r6, r7, r8, pc}</t>
   </si>
@@ -326,9 +326,6 @@
     <t>Burn Heal 0x82</t>
   </si>
   <si>
-    <t>Reduce Damage from Bug, Fire, Flying 0x47</t>
-  </si>
-  <si>
     <t xml:space="preserve">bl 0x00087B58 </t>
   </si>
   <si>
@@ -573,6 +570,78 @@
   </si>
   <si>
     <t>E19400EA</t>
+  </si>
+  <si>
+    <t>Reduce Damage from Fire 0x47</t>
+  </si>
+  <si>
+    <t>push {r4, r5, lr}</t>
+  </si>
+  <si>
+    <t>bl 0x00088874</t>
+  </si>
+  <si>
+    <t>Check if Steel</t>
+  </si>
+  <si>
+    <t>mov r1, 0x8</t>
+  </si>
+  <si>
+    <t>cmp r0, 0x1</t>
+  </si>
+  <si>
+    <t>cmp r9, 0x4F</t>
+  </si>
+  <si>
+    <t>bls 0x000FE300</t>
+  </si>
+  <si>
+    <t>bhi 0x000FE308</t>
+  </si>
+  <si>
+    <t>Defensive Steel Type if not Steel 0x4E/0x4F/0x6D/0xA7/0x6A</t>
+  </si>
+  <si>
+    <t>mov r2, r4</t>
+  </si>
+  <si>
+    <t>000FCDC8</t>
+  </si>
+  <si>
+    <t>30402DE9</t>
+  </si>
+  <si>
+    <t>2D55FEEB</t>
+  </si>
+  <si>
+    <t>0810A0E3</t>
+  </si>
+  <si>
+    <t>A22EFEEB</t>
+  </si>
+  <si>
+    <t>010050E3</t>
+  </si>
+  <si>
+    <t>0500001A</t>
+  </si>
+  <si>
+    <t>0420A0E1</t>
+  </si>
+  <si>
+    <t>3040BDE8</t>
+  </si>
+  <si>
+    <t>4F0059E3</t>
+  </si>
+  <si>
+    <t>3E05009A</t>
+  </si>
+  <si>
+    <t>3F05008A</t>
+  </si>
+  <si>
+    <t>3080BDE8</t>
   </si>
 </sst>
 </file>
@@ -701,8 +770,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1037,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D5FF14-B243-47B9-B921-E1E0A4F7D67F}">
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -1073,13 +1146,13 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -1188,10 +1261,10 @@
         <v>50</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1227,7 +1300,7 @@
         <v>000DB338</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C16" s="5" t="str">
         <f>_xlfn.CONCAT("bne  0x",A$48)</f>
@@ -1247,7 +1320,7 @@
         <v>46</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1295,7 +1368,7 @@
         <v>000DB34C</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C21" s="9" t="str">
         <f>_xlfn.CONCAT("bne  0x",A$48)</f>
@@ -1333,7 +1406,7 @@
         <v>000DB358</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>38</v>
@@ -1381,7 +1454,7 @@
         <v>000DB368</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>31</v>
@@ -1429,7 +1502,7 @@
         <v>000DB378</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>26</v>
@@ -1453,7 +1526,7 @@
         <v>000DB380</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>84</v>
@@ -1480,7 +1553,7 @@
         <v>000DB388</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>21</v>
@@ -1600,7 +1673,7 @@
         <v>000DB3B0</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>2</v>
@@ -1611,7 +1684,7 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>1</v>
@@ -1620,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -1629,7 +1702,7 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="1" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1640,10 +1713,10 @@
         <v>65</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -1680,10 +1753,10 @@
         <v>66</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -1692,10 +1765,10 @@
         <v>000FD260</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D55" s="5"/>
       <c r="F55" s="14"/>
@@ -1719,7 +1792,7 @@
         <v>000FD268</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C57" s="5" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$66)</f>
@@ -1736,10 +1809,10 @@
         <v>61</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="19"/>
@@ -1751,10 +1824,10 @@
         <v>000FD270</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="8"/>
@@ -1770,7 +1843,7 @@
         <v>60</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>71</v>
@@ -1797,13 +1870,13 @@
         <v>000FD27C</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>85</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E62" s="3"/>
     </row>
@@ -1825,7 +1898,7 @@
         <v>000FD284</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C64" s="2" t="str">
         <f>SUBSTITUTE(C51,"push","pop")</f>
@@ -1838,10 +1911,10 @@
         <v>000FD288</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1850,7 +1923,7 @@
         <v>000FD28C</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C66" s="2" t="str">
         <f>SUBSTITUTE(C64,"lr","pc")</f>
@@ -1862,7 +1935,7 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B68" s="4"/>
     </row>
@@ -1872,10 +1945,10 @@
         <v>000FD290</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1911,10 +1984,10 @@
         <v>64</v>
       </c>
       <c r="C72" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="D72" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1923,10 +1996,10 @@
         <v>000FD2A0</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D73" s="5"/>
     </row>
@@ -1949,7 +2022,7 @@
         <v>000FD2A8</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C75" s="5" t="str">
         <f>_xlfn.CONCAT("bne 0x",A$86)</f>
@@ -1969,7 +2042,7 @@
         <v>7</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1991,7 +2064,7 @@
         <v>000FD2B4</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>57</v>
@@ -2004,13 +2077,13 @@
         <v>000FD2B8</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C79" s="21" t="s">
         <v>56</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2019,10 +2092,10 @@
         <v>000FD2BC</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D80" s="21"/>
     </row>
@@ -2032,7 +2105,7 @@
         <v>000FD2C0</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C81" s="21" t="str">
         <f>_xlfn.CONCAT("beq 0x",A86)</f>
@@ -2046,13 +2119,13 @@
         <v>000FD2C4</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D82" s="24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2061,10 +2134,10 @@
         <v>000FD2C8</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D83" s="24"/>
     </row>
@@ -2074,7 +2147,7 @@
         <v>000FD2CC</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C84" s="2" t="str">
         <f>SUBSTITUTE(C69,"push","pop")</f>
@@ -2087,10 +2160,10 @@
         <v>000FD2D0</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2099,7 +2172,7 @@
         <v>000FD2D4</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C86" s="2" t="str">
         <f>SUBSTITUTE(C84,"lr","pc")</f>
@@ -2111,19 +2184,19 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B88" s="4"/>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B89" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="C89" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2132,10 +2205,10 @@
         <v>000FD2DC</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2144,13 +2217,13 @@
         <v>000FD2E0</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2159,13 +2232,13 @@
         <v>000FD2E4</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2173,219 +2246,329 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B94" s="4"/>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="B101" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C101" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="D101" s="27"/>
-    </row>
     <row r="102" spans="1:4">
-      <c r="A102" s="27" t="str">
+      <c r="A102" s="2" t="str">
         <f t="shared" ref="A102:A106" si="6">DEC2HEX(HEX2DEC(A101)+4,8)</f>
         <v>000DDF50</v>
       </c>
-      <c r="B102" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="C102" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="D102" s="27" t="s">
+      <c r="B102" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="103" spans="1:4">
-      <c r="A103" s="27" t="str">
+      <c r="A103" s="2" t="str">
         <f t="shared" si="6"/>
         <v>000DDF54</v>
       </c>
-      <c r="B103" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="C103" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="D103" s="27"/>
+      <c r="B103" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="104" spans="1:4">
-      <c r="A104" s="27" t="str">
+      <c r="A104" s="2" t="str">
         <f t="shared" si="6"/>
         <v>000DDF58</v>
       </c>
-      <c r="B104" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C104" s="27" t="str">
+      <c r="B104" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C104" s="2" t="str">
         <f>SUBSTITUTE(C101,"push","pop")</f>
         <v>pop {lr}</v>
       </c>
-      <c r="D104" s="27"/>
     </row>
     <row r="105" spans="1:4">
-      <c r="A105" s="27" t="str">
+      <c r="A105" s="2" t="str">
         <f t="shared" si="6"/>
         <v>000DDF5C</v>
       </c>
-      <c r="B105" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="C105" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="D105" s="27" t="s">
-        <v>160</v>
+      <c r="B105" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="106" spans="1:4">
-      <c r="A106" s="27" t="str">
+      <c r="A106" s="2" t="str">
         <f t="shared" si="6"/>
         <v>000DDF60</v>
       </c>
-      <c r="B106" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="C106" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="D106" s="27"/>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="27"/>
-      <c r="B107" s="27"/>
-      <c r="C107" s="27"/>
-      <c r="D107" s="27"/>
+      <c r="B106" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="108" spans="1:4">
-      <c r="A108" s="27"/>
-      <c r="B108" s="27"/>
-      <c r="C108" s="27"/>
-      <c r="D108" s="27"/>
+      <c r="A108" s="1" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="109" spans="1:4">
-      <c r="A109" s="27"/>
-      <c r="B109" s="27"/>
-      <c r="C109" s="27"/>
-      <c r="D109" s="27"/>
+      <c r="A109" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="110" spans="1:4">
-      <c r="A110" s="27"/>
-      <c r="B110" s="28"/>
-      <c r="C110" s="27"/>
-      <c r="D110" s="27"/>
+      <c r="A110" s="2" t="str">
+        <f t="shared" ref="A110:A125" si="7">DEC2HEX(HEX2DEC(A109)+4,8)</f>
+        <v>000FCDCC</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="111" spans="1:4">
-      <c r="A111" s="27"/>
-      <c r="B111" s="27"/>
-      <c r="C111" s="27"/>
-      <c r="D111" s="27"/>
+      <c r="A111" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCDD0</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="27"/>
-      <c r="B112" s="28"/>
-      <c r="C112" s="28"/>
-      <c r="D112" s="27"/>
+      <c r="A112" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCDD4</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="113" spans="1:4">
-      <c r="A113" s="27"/>
-      <c r="B113" s="29"/>
-      <c r="C113" s="27"/>
-      <c r="D113" s="27"/>
+      <c r="A113" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCDD8</v>
+      </c>
+      <c r="B113" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D113" s="9"/>
     </row>
     <row r="114" spans="1:4">
-      <c r="A114" s="27"/>
-      <c r="B114" s="29"/>
-      <c r="C114" s="27"/>
-      <c r="D114" s="27"/>
+      <c r="A114" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCDDC</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D114" s="9"/>
     </row>
     <row r="115" spans="1:4">
-      <c r="A115" s="27"/>
-      <c r="B115" s="28"/>
-      <c r="C115" s="27"/>
-      <c r="D115" s="27"/>
+      <c r="A115" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCDE0</v>
+      </c>
+      <c r="B115" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="C115" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="D115" s="21"/>
     </row>
     <row r="116" spans="1:4">
-      <c r="A116" s="27"/>
-      <c r="B116" s="28"/>
-      <c r="C116" s="27"/>
-      <c r="D116" s="27"/>
+      <c r="A116" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCDE4</v>
+      </c>
+      <c r="B116" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C116" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D116" s="21" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="117" spans="1:4">
-      <c r="A117" s="27"/>
-      <c r="B117" s="27"/>
-      <c r="C117" s="27"/>
-      <c r="D117" s="27"/>
+      <c r="A117" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCDE8</v>
+      </c>
+      <c r="B117" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="C117" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="D117" s="21"/>
     </row>
     <row r="118" spans="1:4">
-      <c r="A118" s="27"/>
-      <c r="B118" s="27"/>
-      <c r="C118" s="27"/>
-      <c r="D118" s="27"/>
-    </row>
-    <row r="119" spans="1:4">
-      <c r="A119" s="27"/>
-      <c r="B119" s="27"/>
-      <c r="C119" s="27"/>
-      <c r="D119" s="27"/>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120" s="27"/>
-      <c r="B120" s="27"/>
-      <c r="C120" s="27"/>
-      <c r="D120" s="27"/>
+      <c r="A118" s="21" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCDEC</v>
+      </c>
+      <c r="B118" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="C118" s="21" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A125)</f>
+        <v>bne 0x000FCE08</v>
+      </c>
+      <c r="D118" s="21"/>
+    </row>
+    <row r="119" spans="1:4" s="27" customFormat="1">
+      <c r="A119" s="27" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCDF0</v>
+      </c>
+      <c r="B119" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" s="27" customFormat="1">
+      <c r="A120" s="27" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCDF4</v>
+      </c>
+      <c r="B120" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="C120" s="27" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="121" spans="1:4">
-      <c r="A121" s="27"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="27"/>
-      <c r="D121" s="27"/>
+      <c r="A121" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCDF8</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C121" s="2" t="str">
+        <f>SUBSTITUTE(C109,"push","pop")</f>
+        <v>pop {r4, r5, lr}</v>
+      </c>
     </row>
     <row r="122" spans="1:4">
-      <c r="A122" s="27"/>
-      <c r="B122" s="27"/>
-      <c r="C122" s="27"/>
-      <c r="D122" s="27"/>
+      <c r="A122" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCDFC</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="123" spans="1:4">
-      <c r="A123" s="27"/>
-      <c r="B123" s="27"/>
-      <c r="C123" s="27"/>
-      <c r="D123" s="27"/>
+      <c r="A123" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCE00</v>
+      </c>
+      <c r="B123" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="124" spans="1:4">
-      <c r="A124" s="27"/>
-      <c r="B124" s="27"/>
-      <c r="C124" s="27"/>
-      <c r="D124" s="27"/>
+      <c r="A124" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCE04</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v>000FCE08</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C125" s="2" t="str">
+        <f>SUBSTITUTE(C121,"lr","pc")</f>
+        <v>pop {r4, r5, pc}</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
